--- a/artfynd/A 43620-2023 artfynd.xlsx
+++ b/artfynd/A 43620-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43620-2023 artfynd.xlsx
+++ b/artfynd/A 43620-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1974783</v>
+        <v>877603</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541625.4662358197</v>
+        <v>541625</v>
       </c>
       <c r="R2" t="n">
-        <v>6980797.565093753</v>
+        <v>6980798</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1920729</v>
+        <v>1894582</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541610.4920112141</v>
+        <v>541676</v>
       </c>
       <c r="R3" t="n">
-        <v>6980792.367593641</v>
+        <v>6980722</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,21 +863,11 @@
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,11 +876,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hygge</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -927,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1974784</v>
+        <v>1974783</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541610.4920112141</v>
+        <v>541625</v>
       </c>
       <c r="R4" t="n">
-        <v>6980792.367593641</v>
+        <v>6980798</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,19 +969,9 @@
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-08-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,37 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1894582</v>
+        <v>1974784</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1102,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541676.1079227783</v>
+        <v>541610</v>
       </c>
       <c r="R5" t="n">
-        <v>6980722.202422371</v>
+        <v>6980792</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1135,21 +1080,11 @@
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1158,6 +1093,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1174,37 +1114,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>877603</v>
+        <v>1920729</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1223,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541625.4662358197</v>
+        <v>541610</v>
       </c>
       <c r="R6" t="n">
-        <v>6980797.565093753</v>
+        <v>6980792</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1256,19 +1191,9 @@
           <t>2011-08-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-08-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43620-2023 artfynd.xlsx
+++ b/artfynd/A 43620-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/877603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1894582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1974783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1974784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,8 +1247,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1920729</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>